--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,12 +436,12 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1108,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1149,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 12分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1318,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1873,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1984,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2095,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2206,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2317,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2378,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2428,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2489,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2539,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2600,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2650,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2711,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2761,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2822,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2872,1240 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,17 +689,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -713,17 +709,13 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -892,12 +884,12 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -999,24 +991,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1105,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1235,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1268,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1346,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1490,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1712,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1751,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1823,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,12 +1917,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq44，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1934,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,10 +1958,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2045,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2378,7 +2406,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2517,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2628,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2739,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2850,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +2961,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3072,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3155,7 +3183,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3294,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3377,7 +3405,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3488,7 +3516,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3599,7 +3627,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3710,7 +3738,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3821,7 +3849,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3865,17 +3893,13 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3960,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4051,7 +4075,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4100,12 +4124,694 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
           <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1249,12 +1249,12 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq44，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq50，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq47，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2303,10 +2303,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2406,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2517,7 +2529,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2628,7 +2640,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,7 +2751,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2862,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,7 +2973,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,7 +3084,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,7 +3195,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3294,7 +3306,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,7 +3417,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3516,7 +3528,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3627,7 +3639,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3738,7 +3750,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3849,7 +3861,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3960,7 +3972,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4075,7 +4087,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4190,7 +4202,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4305,7 +4317,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4416,7 +4428,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4531,7 +4543,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4646,7 +4658,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4708,22 +4720,22 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4756,12 +4768,12 @@
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4775,7 +4787,7 @@
       <c r="T38" s="2" t="inlineStr"/>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4810,6 +4822,117 @@
       </c>
       <c r="AB38" s="2" t="inlineStr"/>
       <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
         </is>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1475,24 +1475,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1584,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,17 +1645,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1661,13 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1695,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1728,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1752,17 +1764,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1772,13 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1806,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1839,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1863,33 +1883,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1946,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq50，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq62，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1950,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2073,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,32 +2175,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2184,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2208,33 +2236,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2299,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq47，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq61，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2295,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2385,32 +2417,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2418,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2442,33 +2478,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2568,7 +2608,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2607,32 +2647,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2640,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2664,33 +2708,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2718,32 +2766,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2751,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2775,33 +2827,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2829,32 +2885,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2862,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2886,33 +2946,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2973,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3012,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3084,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3639,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3750,7 +3814,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3861,7 +3925,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3972,7 +4036,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4087,7 +4151,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4141,7 +4205,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4266,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4317,7 +4381,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4428,7 +4492,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4482,7 +4546,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4607,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4597,7 +4661,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4722,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4707,12 +4771,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4837,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4817,13 +4881,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4952,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4928,11 +4996,1038 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr"/>
-      <c r="AC39" s="2" t="inlineStr">
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
         </is>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3115,32 +3115,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3172,33 +3176,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3226,32 +3234,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3259,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,17 +3295,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3303,13 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3337,32 +3353,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3370,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3394,17 +3414,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3414,13 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3448,32 +3472,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3481,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3505,33 +3533,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3559,32 +3591,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3592,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3616,17 +3652,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3636,13 +3672,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3742,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3814,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3853,7 +3893,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3925,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4118,32 +4158,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4151,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4175,37 +4219,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4233,32 +4277,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4266,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4290,27 +4338,27 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4348,12 +4396,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4381,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4389,10 +4437,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4492,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4546,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4574,32 +4638,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4607,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4631,17 +4699,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4651,17 +4719,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4776,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4876,7 +4944,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4891,7 +4959,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4952,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5006,7 +5074,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5121,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5250,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5236,7 +5304,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5365,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5408,7 +5476,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5519,7 +5587,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5573,7 +5641,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5702,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5688,7 +5756,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5817,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5803,7 +5871,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5932,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5918,7 +5986,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5979,7 +6047,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6033,6 +6101,803 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,18 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2378,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2389,7 +2393,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2502,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2623,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2738,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3091,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3563,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3793,7 +3797,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3904,7 +3908,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4019,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4249,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4368,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4405,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4429,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4495,7 +4499,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4523,32 +4527,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4556,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4580,17 +4588,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4600,17 +4608,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4729,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4757,32 +4765,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4790,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4814,37 +4826,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4872,32 +4884,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4905,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4929,17 +4945,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4949,17 +4965,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4987,32 +5003,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5020,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5044,17 +5064,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5064,17 +5084,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5102,32 +5122,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5135,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5159,17 +5183,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5179,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5217,32 +5241,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5250,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5274,17 +5302,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5294,17 +5322,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5332,32 +5360,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5365,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5389,33 +5421,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5526,7 +5562,7 @@
       <c r="AB43" s="2" t="inlineStr"/>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5554,32 +5590,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5587,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5611,17 +5651,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5631,17 +5671,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5756,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5857,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5856,7 +5896,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5871,7 +5911,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5986,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6097,7 +6137,7 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6212,7 +6252,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6313,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6327,7 +6367,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6428,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6438,7 +6478,7 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6539,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6549,7 +6589,7 @@
       <c r="AB52" s="2" t="inlineStr"/>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6650,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6664,7 +6704,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6765,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6779,7 +6819,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6880,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6884,17 +6924,695 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>161.0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>17/28</t>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,18 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,22 +3199,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3858,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3969,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4008,7 +4012,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4134,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4253,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4618,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4856,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4975,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5551,7 +5555,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5627,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5681,7 +5685,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5713,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5742,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,17 +5774,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5786,17 +5794,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5824,32 +5832,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5857,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5881,17 +5893,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5901,17 +5913,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5939,32 +5951,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5972,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5996,17 +6012,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6016,17 +6032,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6054,32 +6070,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6087,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6111,33 +6131,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6165,32 +6189,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6198,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6222,37 +6250,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6280,32 +6308,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6313,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6337,17 +6369,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6357,17 +6389,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6467,7 +6499,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6539,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6650,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6704,7 +6736,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6797,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,7 +6912,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6934,7 +6966,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6995,7 +7027,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7049,7 +7081,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7142,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7221,7 +7253,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7332,7 +7364,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7447,7 +7479,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7558,7 +7590,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7602,17 +7634,580 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>142.0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>10/29</t>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>137.5</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,13 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,13 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4138,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,17 +4250,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4322,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4366,12 +4374,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4622,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,14 +4734,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>137.5</t>
@@ -4741,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4860,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5685,7 +5693,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5923,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6161,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6280,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6427,32 +6435,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6460,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6484,17 +6496,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6504,13 +6516,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6538,32 +6554,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6571,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,17 +6615,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6615,13 +6635,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6649,32 +6673,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6682,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6706,32 +6734,32 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6764,32 +6792,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6797,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6821,17 +6853,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6841,12 +6873,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6879,32 +6911,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6912,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6936,37 +6972,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7081,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7253,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7418,7 +7454,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,7 +7626,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7644,7 +7680,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7816,7 +7852,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7870,7 +7906,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7967,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7985,7 +8021,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8082,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8090,13 +8126,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8157,7 +8197,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8211,6 +8251,351 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6683,24 +6683,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6802,19 +6802,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6921,24 +6921,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7030,32 +7030,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7063,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7087,17 +7091,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7107,17 +7111,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7149,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq40推进至seq52，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7178,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7186,10 +7190,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7289,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7400,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7454,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7626,7 +7642,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7757,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7852,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7967,7 +7983,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8082,7 +8098,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8197,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8308,7 +8324,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8357,12 +8373,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8439,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8477,7 +8493,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8554,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8587,12 +8603,127 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,18 +2025,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2145,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,14 +2259,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>141.5</t>
@@ -2270,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,13 +2391,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,13 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,17 +2744,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,14 +2858,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -2861,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,17 +3216,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,14 +3330,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>152.0</t>
@@ -3333,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3464,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4031,7 +4043,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,7 +4512,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4511,7 +4523,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4875,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4987,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5225,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,14 +5341,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>141.5</t>
@@ -5344,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,13 +5580,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,14 +5813,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -5812,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6764,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7040,24 +7056,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7067,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7116,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7170,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq40推进至seq52，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq40推进至seq57，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7182,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7244,7 +7260,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7272,32 +7288,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7305,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7329,33 +7349,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7383,32 +7407,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7416,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7440,17 +7468,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7460,17 +7488,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7498,32 +7526,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7531,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7555,17 +7587,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7575,13 +7607,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7609,32 +7645,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7642,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7666,17 +7706,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7686,17 +7726,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7724,32 +7764,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7757,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7781,17 +7825,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7801,13 +7845,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7835,32 +7883,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7868,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7892,17 +7944,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7912,17 +7964,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7983,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8037,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8152,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8263,7 +8315,7 @@
       <c r="AB66" s="2" t="inlineStr"/>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8378,7 +8430,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8493,7 +8545,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8608,7 +8660,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8723,7 +8775,689 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -834,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1307,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -1318,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,14 +1545,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -1556,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,14 +1783,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>137.5</t>
@@ -1794,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2220,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2263,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2274,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2390,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2520,7 +2524,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2634,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2873,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3097,17 +3101,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3221,12 +3225,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3345,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3568,14 +3572,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>139.5</t>
@@ -3583,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,14 +3691,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -3702,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,17 +3811,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,7 +3921,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,13 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4158,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,7 +4389,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4457,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,14 +4635,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -4642,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,14 +4873,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -4880,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,14 +5111,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>137.5</t>
@@ -5118,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5349,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5356,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5585,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5828,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6307,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,14 +6416,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>139.5</t>
@@ -6423,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,17 +6540,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,7 +6654,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6726,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,7 +6892,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6964,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7018,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,14 +7130,14 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
           <t>136.3</t>
@@ -7137,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7563,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7602,7 +7610,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7736,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7774,24 +7782,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7801,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,12 +7858,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7893,24 +7901,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7920,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,12 +7977,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8002,32 +8010,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8035,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,17 +8071,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8079,17 +8091,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8117,32 +8129,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8150,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,17 +8190,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8194,17 +8210,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8232,32 +8248,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8265,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,17 +8309,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8309,13 +8329,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB66" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8343,32 +8367,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8376,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8400,17 +8428,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8420,17 +8448,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8545,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8660,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8775,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8898,7 +8926,7 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -8946,12 +8974,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8990,22 +9018,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -9013,22 +9041,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9061,12 +9089,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9105,18 +9133,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB73" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9124,22 +9156,22 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9172,12 +9204,12 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9191,7 +9223,7 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
@@ -9216,7 +9248,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9235,22 +9267,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9283,12 +9315,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9327,22 +9359,18 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -9350,22 +9378,22 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9398,12 +9426,12 @@
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9417,47 +9445,1197 @@
       <c r="T76" s="2" t="inlineStr"/>
       <c r="U76" s="2" t="inlineStr">
         <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
           <t>16:01</t>
         </is>
       </c>
-      <c r="V76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W76" s="2" t="inlineStr">
+      <c r="W77" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X76" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y76" s="2" t="inlineStr">
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z76" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
+      <c r="AB80" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>23/30</t>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3339,17 +3339,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4997,17 +4997,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6897,17 +6897,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8258,24 +8258,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8377,19 +8377,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8486,32 +8486,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8519,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8543,37 +8547,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8601,32 +8605,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8634,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8658,17 +8666,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8678,17 +8686,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8864,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8903,7 +8911,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8946,32 +8954,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8979,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,17 +9015,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9023,17 +9035,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9176,12 +9188,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq42，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -9209,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9217,10 +9229,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q74" s="2" t="inlineStr"/>
-      <c r="R74" s="2" t="inlineStr"/>
-      <c r="S74" s="2" t="inlineStr"/>
-      <c r="T74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -9398,32 +9426,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9431,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9455,17 +9487,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9475,17 +9507,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9661,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9776,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9891,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10006,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10060,7 +10092,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10236,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10290,7 +10322,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10405,7 +10437,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10498,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10581,7 +10613,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10635,7 +10667,812 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,22 +2263,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,22 +3334,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3691,22 +3691,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,14 +6059,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7377,17 +7377,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -8839,32 +8839,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -8872,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8896,17 +8900,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8916,17 +8920,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9045,7 +9049,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -9053,32 +9057,32 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9101,12 +9105,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9114,10 +9118,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -9145,22 +9165,18 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>141.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9168,32 +9184,32 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq42，推进14站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -9216,12 +9232,12 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9229,29 +9245,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q74" s="2" t="inlineStr">
-        <is>
-          <t>物理seq27（站名待映射）</t>
-        </is>
-      </c>
-      <c r="R74" s="2" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="S74" s="2" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="T74" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9287,7 +9287,7 @@
       <c r="AB74" s="2" t="inlineStr"/>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9295,22 +9295,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9387,18 +9387,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9410,7 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -9416,7 +9420,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -9436,24 +9440,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9463,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9477,7 +9481,7 @@
       <c r="T76" s="2" t="inlineStr"/>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
@@ -9502,22 +9506,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9525,60 +9529,64 @@
       <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,37 +9610,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9640,22 +9648,22 @@
       <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9688,12 +9696,12 @@
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9707,7 +9715,7 @@
       <c r="T78" s="2" t="inlineStr"/>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
@@ -9732,22 +9740,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -9755,22 +9763,22 @@
       <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9803,12 +9811,12 @@
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9852,17 +9860,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9878,7 @@
       <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -9880,7 +9888,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -9918,12 +9926,12 @@
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9937,7 +9945,7 @@
       <c r="T80" s="2" t="inlineStr"/>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
@@ -9972,12 +9980,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9985,22 +9993,22 @@
       <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10033,12 +10041,12 @@
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10077,22 +10085,22 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10108,7 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -10110,7 +10118,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -10148,12 +10156,12 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10167,7 +10175,7 @@
       <c r="T82" s="2" t="inlineStr"/>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
@@ -10197,17 +10205,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -10215,22 +10223,22 @@
       <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10263,12 +10271,12 @@
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10312,17 +10320,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10338,7 @@
       <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -10340,7 +10348,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -10378,12 +10386,12 @@
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10397,7 +10405,7 @@
       <c r="T84" s="2" t="inlineStr"/>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
@@ -10422,22 +10430,22 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10445,22 +10453,22 @@
       <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10493,12 +10501,12 @@
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10537,22 +10545,22 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10568,7 @@
       <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -10570,7 +10578,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -10608,12 +10616,12 @@
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10627,7 +10635,7 @@
       <c r="T86" s="2" t="inlineStr"/>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
@@ -10662,12 +10670,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10675,22 +10683,22 @@
       <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10723,12 +10731,12 @@
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10767,7 +10775,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10777,12 +10785,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -10790,7 +10798,7 @@
       <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -10800,7 +10808,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -10838,12 +10846,12 @@
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10857,7 +10865,7 @@
       <c r="T88" s="2" t="inlineStr"/>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
@@ -10887,17 +10895,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -10905,22 +10913,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10953,12 +10961,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11002,17 +11010,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -11020,22 +11028,22 @@
       <c r="A90" s="2" t="inlineStr"/>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -11068,12 +11076,12 @@
       <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11087,7 +11095,7 @@
       <c r="T90" s="2" t="inlineStr"/>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
@@ -11117,17 +11125,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -11135,22 +11143,22 @@
       <c r="A91" s="2" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11183,12 +11191,12 @@
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11237,12 +11245,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11250,22 +11258,22 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11298,12 +11306,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11317,7 +11325,7 @@
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
@@ -11347,17 +11355,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -11365,22 +11373,22 @@
       <c r="A93" s="2" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11413,12 +11421,12 @@
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11432,7 +11440,7 @@
       <c r="T93" s="2" t="inlineStr"/>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
@@ -11457,22 +11465,593 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>8/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>27/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>—/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>26/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB93" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>4/30</t>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>7/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,22 +1783,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,14 +2263,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2390,22 +2390,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,22 +3572,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4878,17 +4878,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,22 +5111,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,14 +5349,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,22 +6416,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,22 +6654,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7135,17 +7135,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,22 +7610,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9625,14 +9625,14 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
           <t>142.7</t>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9668,32 +9668,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9701,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9725,37 +9729,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9855,7 +9859,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9898,32 +9902,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9931,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,37 +9963,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -10013,32 +10021,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10046,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10070,17 +10082,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10090,17 +10102,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10128,32 +10140,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10161,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10185,37 +10201,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -10243,32 +10259,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -10276,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,37 +10320,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10358,32 +10378,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10391,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10415,17 +10439,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10435,17 +10459,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10473,32 +10497,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10506,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10530,37 +10558,37 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10675,7 +10703,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10851,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10905,7 +10933,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10994,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11020,7 +11048,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11109,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11135,7 +11163,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11250,7 +11278,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11339,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11365,7 +11393,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11480,7 +11508,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11656,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11767,7 +11795,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11821,7 +11849,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11910,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11944,22 +11972,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11992,12 +12020,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12011,47 +12039,852 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr">
+      <c r="W99" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X98" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y98" s="2" t="inlineStr">
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z98" s="2" t="inlineStr">
+      <c r="Z99" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA98" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB98" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr">
-        <is>
-          <t>7/31</t>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>11/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>142.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>19/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>10/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>142.7</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>17/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2509,22 +2509,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,22 +2981,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5473,17 +5473,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,22 +5702,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7734,17 +7734,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8329,17 +8329,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8567,17 +8567,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10616,32 +10616,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10649,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10673,37 +10677,37 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA86" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -10731,32 +10735,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10764,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10788,17 +10796,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10808,17 +10816,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10846,32 +10854,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10879,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10903,17 +10915,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10923,17 +10935,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10961,32 +10973,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10994,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11018,17 +11034,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11038,17 +11054,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11076,32 +11092,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11109,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11133,17 +11153,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11153,17 +11173,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11211,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11224,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11248,17 +11272,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11268,17 +11292,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11393,7 +11417,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11445,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11454,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11478,37 +11506,37 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11597,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11684,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11795,7 +11823,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11910,7 +11938,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12025,7 +12053,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12140,7 +12168,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12194,7 +12222,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -12255,7 +12283,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12370,7 +12398,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12424,7 +12452,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -12485,7 +12513,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12539,7 +12567,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -12600,7 +12628,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12715,7 +12743,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12777,22 +12805,22 @@
       <c r="A105" s="2" t="inlineStr"/>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -12825,12 +12853,12 @@
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12844,47 +12872,392 @@
       <c r="T105" s="2" t="inlineStr"/>
       <c r="U105" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>6/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W105" s="2" t="inlineStr">
+      <c r="W106" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X105" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y105" s="2" t="inlineStr">
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z105" s="2" t="inlineStr">
+      <c r="Z106" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA105" s="2" t="inlineStr">
+      <c r="AA106" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB105" s="2" t="inlineStr">
+      <c r="AB106" s="2" t="inlineStr">
         <is>
           <t>139.7</t>
         </is>
       </c>
-      <c r="AC105" s="2" t="inlineStr">
-        <is>
-          <t>17/31</t>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>14/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>19/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>2/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东35路.xlsx
+++ b/data/export/2026-10-20-浦东35路.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3339,17 +3339,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8801,17 +8801,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9392,17 +9392,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9511,17 +9511,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10102,17 +10102,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -10945,7 +10945,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -11417,7 +11417,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11564,32 +11564,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11597,7 +11601,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11621,17 +11625,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11641,17 +11645,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -11679,32 +11683,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -11712,7 +11720,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11736,17 +11744,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11756,13 +11764,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB95" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -11790,32 +11802,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11823,7 +11839,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11847,17 +11863,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11867,17 +11883,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -11905,32 +11921,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11938,7 +11958,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11962,17 +11982,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11982,17 +12002,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -12020,12 +12040,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12053,7 +12073,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12061,10 +12081,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12107,7 +12143,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -12135,32 +12171,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12168,7 +12208,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12192,17 +12232,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12212,17 +12252,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -12250,32 +12290,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12283,7 +12327,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12307,17 +12351,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12327,12 +12371,12 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12398,7 +12442,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12452,7 +12496,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -12480,12 +12524,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq57，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -12513,7 +12557,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12521,10 +12565,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q102" s="2" t="inlineStr"/>
-      <c r="R102" s="2" t="inlineStr"/>
-      <c r="S102" s="2" t="inlineStr"/>
-      <c r="T102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12567,7 +12627,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -12628,7 +12688,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12682,7 +12742,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -12743,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12797,7 +12857,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12918,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12912,7 +12972,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -12973,7 +13033,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13027,7 +13087,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13148,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13142,7 +13202,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -13203,7 +13263,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
